--- a/output/casestudy_20260901.xlsx
+++ b/output/casestudy_20260901.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9.247977800001536</v>
+        <v>8.865853999999672</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.947821400000976</v>
+        <v>9.447161000000051</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.755993799997668</v>
+        <v>5.993135599997913</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>10.08338139999978</v>
+        <v>9.369864399999642</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.70692719999715</v>
+        <v>10.41129130000263</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>6.708703600001172</v>
+        <v>7.162889499999437</v>
       </c>
     </row>
   </sheetData>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9.2 초</t>
+          <t>8.9 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.9 초</t>
+          <t>9.4 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.8 초</t>
+          <t>6.0 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.1 초</t>
+          <t>9.4 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.7 초</t>
+          <t>10.4 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.7 초</t>
+          <t>7.2 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>53.6 초</t>
+          <t>52.4 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260901.xlsx
+++ b/output/casestudy_20260901.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>8.865853999999672</v>
+        <v>8.75281239999822</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>9.447161000000051</v>
+        <v>8.695853699999134</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>5.993135599997913</v>
+        <v>5.154954499997984</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9.369864399999642</v>
+        <v>8.932292800000141</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>10.41129130000263</v>
+        <v>9.891891800001758</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>7.162889499999437</v>
+        <v>6.394270099997811</v>
       </c>
     </row>
   </sheetData>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>69555562.36799997</v>
+        <v>69546898.36799997</v>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.9 초</t>
+          <t>8.8 초</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.4 초</t>
+          <t>8.7 초</t>
         </is>
       </c>
     </row>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.0 초</t>
+          <t>5.2 초</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.4 초</t>
+          <t>8.9 초</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.4 초</t>
+          <t>9.9 초</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7.2 초</t>
+          <t>6.4 초</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>52.4 초</t>
+          <t>48.9 초</t>
         </is>
       </c>
     </row>
